--- a/data/trans_dic/P3A$otraSIcobraNOhogar-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobraNOhogar-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,59</t>
+          <t>0,64; 2,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,54</t>
+          <t>0,47; 1,48</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,84</t>
+          <t>0,22; 1,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,44</t>
+          <t>0,61; 2,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,69</t>
+          <t>0,57; 1,81</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,7</t>
+          <t>0,42; 2,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,93</t>
+          <t>2,16; 6,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,11</t>
+          <t>0,71; 3,14</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,99</t>
+          <t>1,77; 3,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,91</t>
+          <t>0,58; 1,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,66</t>
+          <t>1,3; 2,68</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,69</t>
+          <t>1,32; 3,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,0</t>
+          <t>1,97; 3,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,4</t>
+          <t>2,01; 3,48</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,36</t>
+          <t>3,22; 5,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,19</t>
+          <t>2,41; 4,03</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,25</t>
+          <t>1,25; 2,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,7</t>
+          <t>1,84; 2,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,36</t>
+          <t>1,67; 2,34</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3677; 13103</t>
+          <t>3216; 12285</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4057</t>
+          <t>0; 3995</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4438; 14706</t>
+          <t>4504; 14072</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1008; 8316</t>
+          <t>995; 8215</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2061; 9349</t>
+          <t>2344; 9851</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4490; 14062</t>
+          <t>4792; 15130</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2934; 18071</t>
+          <t>2777; 19637</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3524; 11520</t>
+          <t>3586; 11390</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5420; 25957</t>
+          <t>5956; 26209</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19102; 41259</t>
+          <t>18327; 40347</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5641; 18714</t>
+          <t>5703; 18832</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26250; 53603</t>
+          <t>26219; 53978</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6020; 17514</t>
+          <t>6280; 17684</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17970; 33627</t>
+          <t>16575; 31937</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26408; 44714</t>
+          <t>26456; 45864</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4080</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23861; 40782</t>
+          <t>24497; 40544</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24219; 41994</t>
+          <t>24165; 40361</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>42349; 75991</t>
+          <t>42282; 73563</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>64848; 96718</t>
+          <t>65883; 98187</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>115277; 163946</t>
+          <t>116202; 162816</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$otraSIcobraNOhogar-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobraNOhogar-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,43</t>
+          <t>0,65; 2,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,48</t>
+          <t>0,42; 1,39</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,82</t>
+          <t>0,2; 1,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,57</t>
+          <t>0,64; 2,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,81</t>
+          <t>0,53; 1,74</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,94</t>
+          <t>1,23; 3,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,85</t>
+          <t>2,27; 7,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,14</t>
+          <t>1,85; 4,08</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,9</t>
+          <t>1,78; 3,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,93</t>
+          <t>1,09; 2,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,68</t>
+          <t>1,69; 2,89</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,72</t>
+          <t>1,12; 3,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,8</t>
+          <t>2,41; 4,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,48</t>
+          <t>2,08; 3,38</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,33</t>
+          <t>3,02; 5,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,03</t>
+          <t>2,34; 4,01</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,18</t>
+          <t>1,39; 2,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 2,75</t>
+          <t>2,05; 2,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,34</t>
+          <t>1,85; 2,42</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8618</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3216; 12285</t>
+          <t>3594; 14719</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3995</t>
+          <t>0; 4213</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4504; 14072</t>
+          <t>4371; 14472</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>9064</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>995; 8215</t>
+          <t>966; 8654</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2344; 9851</t>
+          <t>2704; 9919</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4792; 15130</t>
+          <t>4841; 15793</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9584</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16227</t>
+          <t>18007</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2777; 19637</t>
+          <t>5810; 16499</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3586; 11390</t>
+          <t>4235; 13846</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5956; 26209</t>
+          <t>12180; 26845</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>26977</t>
+          <t>29277</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12340</t>
+          <t>13716</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39317</t>
+          <t>42993</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18327; 40347</t>
+          <t>20143; 44402</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5703; 18832</t>
+          <t>9378; 20309</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26219; 53978</t>
+          <t>33719; 57645</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>11697</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24974</t>
+          <t>25724</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35480</t>
+          <t>37421</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6280; 17684</t>
+          <t>6388; 18629</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16575; 31937</t>
+          <t>19987; 33891</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26456; 45864</t>
+          <t>29048; 47289</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>31304</t>
+          <t>33185</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31304</t>
+          <t>33185</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24497; 40544</t>
+          <t>25472; 43147</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24165; 40361</t>
+          <t>25274; 43421</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>57508</t>
+          <t>61849</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>81510</t>
+          <t>87440</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>139018</t>
+          <t>149289</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>42282; 73563</t>
+          <t>47741; 77038</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>65883; 98187</t>
+          <t>74412; 101556</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>116202; 162816</t>
+          <t>130865; 170970</t>
         </is>
       </c>
     </row>
